--- a/Planilhas/Pedidos Conta do Razão.xlsx
+++ b/Planilhas/Pedidos Conta do Razão.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python_scripts\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAE00B8-01E1-4BF3-A57F-043DCEFA9195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6676DC-1B5D-4CC2-8115-8184A3E23016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28635" yWindow="-135" windowWidth="29130" windowHeight="15810" xr2:uid="{B22F4247-8A78-4CA2-917D-234C68224E18}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{B22F4247-8A78-4CA2-917D-234C68224E18}"/>
   </bookViews>
   <sheets>
     <sheet name="ALTERAR PARA F5" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="7">
   <si>
     <t>Item</t>
   </si>
@@ -194,8 +194,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}" name="Tabela1" displayName="Tabela1" ref="A1:E37" totalsRowShown="0" dataDxfId="4">
-  <autoFilter ref="A1:E37" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}" name="Tabela1" displayName="Tabela1" ref="A1:E13" totalsRowShown="0" dataDxfId="4">
+  <autoFilter ref="A1:E13" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{D0BC8C79-FDF1-4144-B598-1BCD4BB7CFD1}" name="Pedidos"/>
     <tableColumn id="2" xr3:uid="{3D9316E3-CFBE-4A9E-8B75-E0BF8E30E135}" name="Item" dataDxfId="3"/>
@@ -504,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C176DAE8-01D4-4562-9DC5-3FF54C0846F5}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.81640625" style="1" bestFit="1" customWidth="1"/>
@@ -533,7 +533,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>4500037299</v>
+        <v>4500039163</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -550,7 +550,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>4500037298</v>
+        <v>4500039164</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -566,8 +566,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>4500037297</v>
+      <c r="A4" s="1">
+        <v>4500039165</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -583,8 +583,8 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>4500037296</v>
+      <c r="A5" s="1">
+        <v>4500039166</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -600,8 +600,8 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>4500037295</v>
+      <c r="A6" s="1">
+        <v>4500039167</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -617,8 +617,8 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>4500037294</v>
+      <c r="A7" s="1">
+        <v>4500039168</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -634,8 +634,8 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>4500037292</v>
+      <c r="A8" s="1">
+        <v>4500039169</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -651,8 +651,8 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>4500037291</v>
+      <c r="A9" s="1">
+        <v>4500039171</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -668,8 +668,8 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>4500037290</v>
+      <c r="A10" s="1">
+        <v>4500039172</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -685,8 +685,8 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>4500037287</v>
+      <c r="A11" s="1">
+        <v>4500039176</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -702,8 +702,8 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>4500037286</v>
+      <c r="A12" s="1">
+        <v>4500039177</v>
       </c>
       <c r="B12">
         <v>10</v>
@@ -719,8 +719,8 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>4500037285</v>
+      <c r="A13" s="1">
+        <v>4500039178</v>
       </c>
       <c r="B13">
         <v>10</v>
@@ -732,414 +732,6 @@
         <v>3201010111</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>4500037281</v>
-      </c>
-      <c r="B14">
-        <v>10</v>
-      </c>
-      <c r="C14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14">
-        <v>3201010111</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>4500037280</v>
-      </c>
-      <c r="B15">
-        <v>10</v>
-      </c>
-      <c r="C15" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15">
-        <v>3201010111</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>4500037105</v>
-      </c>
-      <c r="B16">
-        <v>10</v>
-      </c>
-      <c r="C16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16">
-        <v>3201010111</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>4500037102</v>
-      </c>
-      <c r="B17">
-        <v>10</v>
-      </c>
-      <c r="C17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17">
-        <v>3201010111</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>4500037101</v>
-      </c>
-      <c r="B18">
-        <v>10</v>
-      </c>
-      <c r="C18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18">
-        <v>3201010111</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>4500037099</v>
-      </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
-      <c r="C19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19">
-        <v>3201010111</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>4500037098</v>
-      </c>
-      <c r="B20">
-        <v>10</v>
-      </c>
-      <c r="C20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20">
-        <v>3201010111</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>4500037097</v>
-      </c>
-      <c r="B21">
-        <v>10</v>
-      </c>
-      <c r="C21" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21">
-        <v>3201010111</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>4500037093</v>
-      </c>
-      <c r="B22">
-        <v>10</v>
-      </c>
-      <c r="C22" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22">
-        <v>3201010111</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>4500037089</v>
-      </c>
-      <c r="B23">
-        <v>10</v>
-      </c>
-      <c r="C23" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23">
-        <v>3201010111</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>4500037084</v>
-      </c>
-      <c r="B24">
-        <v>10</v>
-      </c>
-      <c r="C24" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24">
-        <v>3201010111</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>4500037081</v>
-      </c>
-      <c r="B25">
-        <v>10</v>
-      </c>
-      <c r="C25" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25">
-        <v>3201010111</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>4500037080</v>
-      </c>
-      <c r="B26">
-        <v>10</v>
-      </c>
-      <c r="C26" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26">
-        <v>3201010111</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>4500037079</v>
-      </c>
-      <c r="B27">
-        <v>10</v>
-      </c>
-      <c r="C27" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27">
-        <v>3201010111</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>4500037078</v>
-      </c>
-      <c r="B28">
-        <v>10</v>
-      </c>
-      <c r="C28" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28">
-        <v>3201010111</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>4500037075</v>
-      </c>
-      <c r="B29">
-        <v>10</v>
-      </c>
-      <c r="C29" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29">
-        <v>3201010111</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>4500037074</v>
-      </c>
-      <c r="B30">
-        <v>10</v>
-      </c>
-      <c r="C30" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30">
-        <v>3201010111</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>4500037071</v>
-      </c>
-      <c r="B31">
-        <v>10</v>
-      </c>
-      <c r="C31" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31">
-        <v>3201010111</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>4500037070</v>
-      </c>
-      <c r="B32">
-        <v>10</v>
-      </c>
-      <c r="C32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32">
-        <v>3201010111</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>4500037067</v>
-      </c>
-      <c r="B33">
-        <v>10</v>
-      </c>
-      <c r="C33" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33">
-        <v>3201010111</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>4500037066</v>
-      </c>
-      <c r="B34">
-        <v>10</v>
-      </c>
-      <c r="C34" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34">
-        <v>3201010111</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>4500037060</v>
-      </c>
-      <c r="B35">
-        <v>10</v>
-      </c>
-      <c r="C35" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35">
-        <v>3201010111</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>4500037059</v>
-      </c>
-      <c r="B36">
-        <v>10</v>
-      </c>
-      <c r="C36" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36">
-        <v>3201010111</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>4500037056</v>
-      </c>
-      <c r="B37">
-        <v>10</v>
-      </c>
-      <c r="C37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37">
-        <v>3201010111</v>
-      </c>
-      <c r="E37" s="2" t="s">
         <v>6</v>
       </c>
     </row>
